--- a/data/dividends_info_20260727.xlsx
+++ b/data/dividends_info_20260727.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47.66999816894531</v>
+        <v>45.8849983215332</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1887979934067432</v>
+        <v>0.1961425374135063</v>
       </c>
       <c r="J2" t="n">
         <v>231</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>65.34999847412109</v>
+        <v>65.15000152587891</v>
       </c>
       <c r="I3" t="n">
-        <v>1.071155342531803</v>
+        <v>1.07444356654688</v>
       </c>
       <c r="J3" t="n">
         <v>210</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6622516249567504</v>
       </c>
       <c r="J4" t="n">
         <v>140</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47.66999816894531</v>
+        <v>45.8849983215332</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1887979934067432</v>
+        <v>0.1961425374135063</v>
       </c>
       <c r="J6" t="n">
         <v>140</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.069999933242798</v>
+        <v>2.065000057220459</v>
       </c>
       <c r="I7" t="n">
-        <v>3.719806883248261</v>
+        <v>3.728813455997861</v>
       </c>
       <c r="J7" t="n">
         <v>119</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>22.10000038146973</v>
+        <v>22.39999961853027</v>
       </c>
       <c r="I8" t="n">
-        <v>1.221719435925386</v>
+        <v>1.205357163384253</v>
       </c>
       <c r="J8" t="n">
         <v>119</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6.059999942779541</v>
+        <v>6</v>
       </c>
       <c r="I9" t="n">
-        <v>3.300330064166073</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J9" t="n">
         <v>112</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.699999809265137</v>
+        <v>7.75</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7792207985226717</v>
+        <v>0.7741935483870968</v>
       </c>
       <c r="J10" t="n">
         <v>84</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="I13" t="n">
-        <v>0.76</v>
+        <v>0.7480315072972982</v>
       </c>
       <c r="J13" t="n">
         <v>63</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>22.10000038146973</v>
+        <v>22.39999961853027</v>
       </c>
       <c r="I14" t="n">
-        <v>1.221719435925386</v>
+        <v>1.205357163384253</v>
       </c>
       <c r="J14" t="n">
         <v>56</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>47.66999816894531</v>
+        <v>45.8849983215332</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1887979934067432</v>
+        <v>0.1961425374135063</v>
       </c>
       <c r="J15" t="n">
         <v>56</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>91.80000305175781</v>
+        <v>92.69999694824219</v>
       </c>
       <c r="I16" t="n">
-        <v>1.44880169475608</v>
+        <v>1.43473575381301</v>
       </c>
       <c r="J16" t="n">
         <v>56</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>5.599999904632568</v>
+        <v>5.619999885559082</v>
       </c>
       <c r="I17" t="n">
-        <v>5.357142948374458</v>
+        <v>5.338078400515052</v>
       </c>
       <c r="J17" t="n">
         <v>49</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2.759999990463257</v>
+        <v>2.799999952316284</v>
       </c>
       <c r="I19" t="n">
-        <v>7.971014520296202</v>
+        <v>7.857142990949205</v>
       </c>
       <c r="J19" t="n">
         <v>14</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>5.079999923706055</v>
       </c>
       <c r="I20" t="n">
-        <v>0.76</v>
+        <v>0.7480315072972982</v>
       </c>
       <c r="J20" t="n">
         <v>7</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>2.900000095367432</v>
+        <v>2.990000009536743</v>
       </c>
       <c r="I21" t="n">
-        <v>5.10237914255145</v>
+        <v>4.94879597083766</v>
       </c>
       <c r="J21" t="n">
         <v>7</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>4.130000114440918</v>
+        <v>4.039999961853027</v>
       </c>
       <c r="I23" t="n">
-        <v>3.38983041454351</v>
+        <v>3.465346567374377</v>
       </c>
       <c r="J23" t="n">
         <v>-7</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>10.02600002288818</v>
+        <v>9.965999603271484</v>
       </c>
       <c r="I24" t="n">
-        <v>2.593257524500803</v>
+        <v>2.60887026239346</v>
       </c>
       <c r="J24" t="n">
         <v>-7</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>13.69999980926514</v>
+        <v>13.4399995803833</v>
       </c>
       <c r="I25" t="n">
-        <v>4.379562104768991</v>
+        <v>4.464285853667328</v>
       </c>
       <c r="J25" t="n">
         <v>-7</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2.667999982833862</v>
+        <v>2.645999908447266</v>
       </c>
       <c r="I26" t="n">
-        <v>8.245877114523935</v>
+        <v>8.314437173548548</v>
       </c>
       <c r="J26" t="n">
         <v>-7</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>6.510000228881836</v>
+        <v>6.414999961853027</v>
       </c>
       <c r="I28" t="n">
-        <v>1.536098256284948</v>
+        <v>1.558846462894041</v>
       </c>
       <c r="J28" t="n">
         <v>-7</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>18.04999923706055</v>
+        <v>18.85000038146973</v>
       </c>
       <c r="I29" t="n">
-        <v>2.083102581123609</v>
+        <v>1.99469491984532</v>
       </c>
       <c r="J29" t="n">
         <v>-7</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2.119999885559082</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I34" t="n">
-        <v>4.009434178699683</v>
+        <v>4.047619231433834</v>
       </c>
       <c r="J34" t="n">
         <v>-21</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>4.269999980926514</v>
+        <v>4.400000095367432</v>
       </c>
       <c r="I35" t="n">
-        <v>1.639344269617801</v>
+        <v>1.590909056427066</v>
       </c>
       <c r="J35" t="n">
         <v>-21</v>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>33.29999923706055</v>
+        <v>33.25</v>
       </c>
       <c r="I36" t="n">
-        <v>0.4504504607707636</v>
+        <v>0.4511278195488721</v>
       </c>
       <c r="J36" t="n">
         <v>-21</v>
@@ -3774,7 +3774,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3784,14 +3784,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3808,7 +3808,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>AEDES S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3818,7 +3818,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -3852,14 +3852,14 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>AEDES S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3869,14 +3869,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3903,14 +3903,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4012,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4022,7 +4022,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4046,7 +4046,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4056,14 +4056,14 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4107,14 +4107,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4124,14 +4124,14 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4141,14 +4141,14 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4175,14 +4175,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4209,14 +4209,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4226,14 +4226,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4243,14 +4243,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4260,14 +4260,14 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4277,14 +4277,14 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4294,14 +4294,14 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4311,14 +4311,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4335,7 +4335,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4345,14 +4345,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4362,14 +4362,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>CIR S.p.A. - COMPAGNIE INDUSTRIALI RIUNITE</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4386,7 +4386,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4403,7 +4403,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4413,14 +4413,14 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4430,14 +4430,14 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4454,7 +4454,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4471,7 +4471,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4481,14 +4481,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4498,14 +4498,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4515,14 +4515,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4532,14 +4532,14 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4556,7 +4556,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -4566,14 +4566,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -4590,7 +4590,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -4607,7 +4607,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4624,7 +4624,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4641,7 +4641,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4658,7 +4658,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -4692,7 +4692,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4736,14 +4736,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4753,14 +4753,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4777,7 +4777,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -4794,7 +4794,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4811,7 +4811,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4828,7 +4828,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4838,14 +4838,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4855,14 +4855,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4896,7 +4896,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4947,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4957,14 +4957,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4981,7 +4981,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4991,14 +4991,14 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5015,7 +5015,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5025,14 +5025,14 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5042,14 +5042,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5059,14 +5059,14 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5076,14 +5076,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5100,7 +5100,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5117,7 +5117,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5127,14 +5127,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5144,14 +5144,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -5168,7 +5168,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -5185,7 +5185,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Masi Agricola S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -5219,7 +5219,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -5229,14 +5229,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Masi Agricola S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -5253,7 +5253,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -5270,7 +5270,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -5287,7 +5287,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -5304,7 +5304,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -5314,14 +5314,14 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Abitare In S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -5331,14 +5331,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -5348,14 +5348,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Half Year Preliminary Results</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -5389,7 +5389,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -5399,14 +5399,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -5416,14 +5416,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -5433,14 +5433,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -5457,7 +5457,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Abitare In S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -5467,14 +5467,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -5484,14 +5484,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -5508,7 +5508,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -5518,14 +5518,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Half Year Preliminary Results</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -5542,7 +5542,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -5559,7 +5559,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -5665,44 +5665,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>doValue S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>